--- a/6.30日订单.xlsx
+++ b/6.30日订单.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14561" uniqueCount="3413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15393" uniqueCount="3620">
   <si>
     <t>选购商品</t>
   </si>
@@ -10266,6 +10266,627 @@
   </si>
   <si>
     <t xml:space="preserve">	2026-06-30 00:02:21</t>
+  </si>
+  <si>
+    <t>【自营】REDMI Watch 6 澎湃OS 3 心率血氧监测蓝牙通话智能手表6-迷雾蓝-(68712)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:59:31</t>
+  </si>
+  <si>
+    <t>小米手表官方直播间</t>
+  </si>
+  <si>
+    <t>【自营】REDMI Watch 6 澎湃OS 3 心率血氧监测蓝牙通话智能手表6-皎月银-(68703)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:57:02</t>
+  </si>
+  <si>
+    <t>【自营】REDMI Watch 6 澎湃OS 3 心率血氧监测蓝牙通话智能手表6-典雅黑-(68698)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:56:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:55:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:48:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:27:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:25:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:24:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:21:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:17:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:14:08</t>
+  </si>
+  <si>
+    <t>【自营国补】Xiaomi Watch 5 全智能旗舰手表智能手势控制小米手表5-eSIM 柔雾蓝真皮表带款-(65344)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:13:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:12:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 23:11:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:59:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:57:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:54:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:51:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:45:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:45:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:40:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:35:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:35:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:29:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:29:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:24:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:23:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:10:48</t>
+  </si>
+  <si>
+    <t>【自营加黑】REDMI Watch 6 心率血氧监测蓝牙通话 智能手表6-典雅黑-(68698)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:09:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:09:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:08:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:08:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:04:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 22:04:30</t>
+  </si>
+  <si>
+    <t>小方头磁吸充电线2-默认-(44917)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:59:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:58:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:56:51</t>
+  </si>
+  <si>
+    <t>【自营加黑】REDMI Watch 6 心率血氧监测蓝牙通话 智能手表6-皎月银-(68703)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:55:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:54:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:49:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:45:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:44:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:37:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:34:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:32:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:31:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:29:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:27:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:24:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:22:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:18:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:18:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:16:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 21:00:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 20:58:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 20:54:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 20:51:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 20:47:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 20:46:42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 20:45:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 20:42:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 20:33:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 20:32:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 20:19:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 20:11:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:53:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:50:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:49:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:44:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:36:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:31:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:28:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:20:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:19:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:16:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:11:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:09:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 19:00:58</t>
+  </si>
+  <si>
+    <t>【自营】Xiaomi Watch S5 时尚新品智能手表 长续航 澎湃OS3-Xiaomi Watch S5 46mm eSIM版-(70282)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 18:55:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 18:39:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 18:26:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 18:24:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 18:19:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 18:13:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 18:01:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 17:57:42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 17:50:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 17:49:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 17:44:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 17:39:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 17:38:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 17:33:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 17:27:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 17:20:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 17:10:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 17:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 16:59:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 16:45:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 16:41:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 16:40:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 16:39:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 16:30:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 16:23:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 16:22:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 16:16:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 16:10:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 16:04:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 15:59:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 15:54:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 15:51:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 15:41:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 15:17:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 15:12:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 15:05:54</t>
+  </si>
+  <si>
+    <t>【新品】Xiaomi Tag 智能定位 适配澎湃 OS 3小米手机 适配iPhone-Xiaomi Tag -(72751)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 14:37:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 14:21:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 14:19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 13:56:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 13:28:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 13:14:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 13:13:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 13:13:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 13:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 13:06:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:58:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:58:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:55:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:53:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:44:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:40:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:30:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:26:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:23:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:18:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:03:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 12:00:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 11:58:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 11:55:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 11:36:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 11:34:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 11:18:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 11:16:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 11:15:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 11:01:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:55:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:36:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:35:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:28:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:26:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:18:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:13:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:11:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:07:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:06:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:00:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 10:00:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:59:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:54:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:52:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:45:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:45:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:36:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:34:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:31:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:29:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:27:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:24:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:22:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:08:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 09:06:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 08:31:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 08:14:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 08:12:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 07:59:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 07:49:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 07:41:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 07:29:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 07:24:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 02:01:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 02:01:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 01:50:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 01:39:42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 01:30:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 01:20:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 01:18:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 01:17:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 01:11:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 00:47:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 00:44:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 00:39:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 00:37:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 00:30:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 00:26:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 00:22:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 00:03:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	2026-06-30 00:03:14</t>
   </si>
 </sst>
 </file>
@@ -10881,11 +11502,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11413,7 +12040,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E3640"/>
+  <dimension ref="A1:E3848"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="9.375"/>
@@ -73299,6 +73926,3542 @@
         <v>3354</v>
       </c>
     </row>
+    <row r="3641" spans="1:5">
+      <c r="A3641" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3641" s="2" t="s">
+        <v>3414</v>
+      </c>
+      <c r="C3641" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3641" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3641" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3642" spans="1:5">
+      <c r="A3642" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3642" s="2" t="s">
+        <v>3417</v>
+      </c>
+      <c r="C3642" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3642" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3642" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3643" spans="1:5">
+      <c r="A3643" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3643" s="2" t="s">
+        <v>3419</v>
+      </c>
+      <c r="C3643" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3643" s="2">
+        <v>580</v>
+      </c>
+      <c r="E3643" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3644" spans="1:5">
+      <c r="A3644" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3644" s="2" t="s">
+        <v>3420</v>
+      </c>
+      <c r="C3644" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3644" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3644" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3645" spans="1:5">
+      <c r="A3645" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3645" s="2" t="s">
+        <v>3421</v>
+      </c>
+      <c r="C3645" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3645" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3645" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3646" spans="1:5">
+      <c r="A3646" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3646" s="2" t="s">
+        <v>3422</v>
+      </c>
+      <c r="C3646" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3646" s="2">
+        <v>536.4</v>
+      </c>
+      <c r="E3646" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3647" spans="1:5">
+      <c r="A3647" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3647" s="2" t="s">
+        <v>3423</v>
+      </c>
+      <c r="C3647" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3647" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3647" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3648" spans="1:5">
+      <c r="A3648" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3648" s="2" t="s">
+        <v>3424</v>
+      </c>
+      <c r="C3648" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3648" s="2">
+        <v>415.8</v>
+      </c>
+      <c r="E3648" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3649" spans="1:5">
+      <c r="A3649" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3649" s="2" t="s">
+        <v>3425</v>
+      </c>
+      <c r="C3649" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3649" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3649" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3650" spans="1:5">
+      <c r="A3650" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3650" s="2" t="s">
+        <v>3426</v>
+      </c>
+      <c r="C3650" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3650" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3650" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3651" spans="1:5">
+      <c r="A3651" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3651" s="2" t="s">
+        <v>3427</v>
+      </c>
+      <c r="C3651" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3651" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3651" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3652" spans="1:5">
+      <c r="A3652" s="2" t="s">
+        <v>3428</v>
+      </c>
+      <c r="B3652" s="2" t="s">
+        <v>3429</v>
+      </c>
+      <c r="C3652" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3652" s="3">
+        <v>2299</v>
+      </c>
+      <c r="E3652" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3653" spans="1:5">
+      <c r="A3653" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3653" s="2" t="s">
+        <v>3430</v>
+      </c>
+      <c r="C3653" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3653" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3653" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3654" spans="1:5">
+      <c r="A3654" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3654" s="2" t="s">
+        <v>3431</v>
+      </c>
+      <c r="C3654" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3654" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3654" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3655" spans="1:5">
+      <c r="A3655" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3655" s="2" t="s">
+        <v>3432</v>
+      </c>
+      <c r="C3655" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3655" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3655" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3656" spans="1:5">
+      <c r="A3656" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3656" s="2" t="s">
+        <v>3433</v>
+      </c>
+      <c r="C3656" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3656" s="2">
+        <v>537.3</v>
+      </c>
+      <c r="E3656" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3657" spans="1:5">
+      <c r="A3657" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3657" s="2" t="s">
+        <v>3434</v>
+      </c>
+      <c r="C3657" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3657" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3657" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3658" spans="1:5">
+      <c r="A3658" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3658" s="2" t="s">
+        <v>3435</v>
+      </c>
+      <c r="C3658" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3658" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3658" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3659" spans="1:5">
+      <c r="A3659" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3659" s="2" t="s">
+        <v>3436</v>
+      </c>
+      <c r="C3659" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3659" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3659" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3660" spans="1:5">
+      <c r="A3660" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3660" s="2" t="s">
+        <v>3437</v>
+      </c>
+      <c r="C3660" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3660" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3660" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3661" spans="1:5">
+      <c r="A3661" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3661" s="2" t="s">
+        <v>3438</v>
+      </c>
+      <c r="C3661" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3661" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3661" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3662" spans="1:5">
+      <c r="A3662" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B3662" s="2" t="s">
+        <v>3439</v>
+      </c>
+      <c r="C3662" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3662" s="2">
+        <v>372</v>
+      </c>
+      <c r="E3662" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3663" spans="1:5">
+      <c r="A3663" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3663" s="2" t="s">
+        <v>3440</v>
+      </c>
+      <c r="C3663" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3663" s="2">
+        <v>528.3</v>
+      </c>
+      <c r="E3663" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3664" spans="1:5">
+      <c r="A3664" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3664" s="2" t="s">
+        <v>3441</v>
+      </c>
+      <c r="C3664" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3664" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3664" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3665" spans="1:5">
+      <c r="A3665" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3665" s="2" t="s">
+        <v>3442</v>
+      </c>
+      <c r="C3665" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3665" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3665" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3666" spans="1:5">
+      <c r="A3666" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3666" s="2" t="s">
+        <v>3443</v>
+      </c>
+      <c r="C3666" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3666" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3666" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3667" spans="1:5">
+      <c r="A3667" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3667" s="2" t="s">
+        <v>3444</v>
+      </c>
+      <c r="C3667" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3667" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3667" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3668" spans="1:5">
+      <c r="A3668" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3668" s="2" t="s">
+        <v>3445</v>
+      </c>
+      <c r="C3668" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3668" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3668" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3669" spans="1:5">
+      <c r="A3669" s="2" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B3669" s="2" t="s">
+        <v>3447</v>
+      </c>
+      <c r="C3669" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3669" s="2">
+        <v>574</v>
+      </c>
+      <c r="E3669" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3670" spans="1:5">
+      <c r="A3670" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3670" s="2" t="s">
+        <v>3448</v>
+      </c>
+      <c r="C3670" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3670" s="2">
+        <v>596.4</v>
+      </c>
+      <c r="E3670" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3671" spans="1:5">
+      <c r="A3671" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3671" s="2" t="s">
+        <v>3449</v>
+      </c>
+      <c r="C3671" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3671" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3671" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3672" spans="1:5">
+      <c r="A3672" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3672" s="2" t="s">
+        <v>3450</v>
+      </c>
+      <c r="C3672" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3672" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3672" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3673" spans="1:5">
+      <c r="A3673" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B3673" s="2" t="s">
+        <v>3451</v>
+      </c>
+      <c r="C3673" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3673" s="2">
+        <v>269</v>
+      </c>
+      <c r="E3673" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3674" spans="1:5">
+      <c r="A3674" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B3674" s="2" t="s">
+        <v>3452</v>
+      </c>
+      <c r="C3674" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3674" s="2">
+        <v>399</v>
+      </c>
+      <c r="E3674" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3675" spans="1:5">
+      <c r="A3675" s="2" t="s">
+        <v>3453</v>
+      </c>
+      <c r="B3675" s="2" t="s">
+        <v>3454</v>
+      </c>
+      <c r="C3675" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3675" s="2">
+        <v>19.9</v>
+      </c>
+      <c r="E3675" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3676" spans="1:5">
+      <c r="A3676" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B3676" s="2" t="s">
+        <v>3455</v>
+      </c>
+      <c r="C3676" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3676" s="2">
+        <v>238</v>
+      </c>
+      <c r="E3676" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3677" spans="1:5">
+      <c r="A3677" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B3677" s="2" t="s">
+        <v>3456</v>
+      </c>
+      <c r="C3677" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3677" s="2">
+        <v>399</v>
+      </c>
+      <c r="E3677" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3678" spans="1:5">
+      <c r="A3678" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3678" s="2" t="s">
+        <v>3458</v>
+      </c>
+      <c r="C3678" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3678" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3678" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3679" spans="1:5">
+      <c r="A3679" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3679" s="2" t="s">
+        <v>3459</v>
+      </c>
+      <c r="C3679" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3679" s="2">
+        <v>531.9</v>
+      </c>
+      <c r="E3679" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3680" spans="1:5">
+      <c r="A3680" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3680" s="2" t="s">
+        <v>3460</v>
+      </c>
+      <c r="C3680" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3680" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3680" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3681" spans="1:5">
+      <c r="A3681" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B3681" s="2" t="s">
+        <v>3461</v>
+      </c>
+      <c r="C3681" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3681" s="2">
+        <v>268.8</v>
+      </c>
+      <c r="E3681" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3682" spans="1:5">
+      <c r="A3682" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3682" s="2" t="s">
+        <v>3462</v>
+      </c>
+      <c r="C3682" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3682" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3682" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3683" spans="1:5">
+      <c r="A3683" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3683" s="2" t="s">
+        <v>3463</v>
+      </c>
+      <c r="C3683" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3683" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3683" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3684" spans="1:5">
+      <c r="A3684" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3684" s="2" t="s">
+        <v>3464</v>
+      </c>
+      <c r="C3684" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3684" s="2">
+        <v>589</v>
+      </c>
+      <c r="E3684" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3685" spans="1:5">
+      <c r="A3685" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3685" s="2" t="s">
+        <v>3465</v>
+      </c>
+      <c r="C3685" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3685" s="2">
+        <v>549</v>
+      </c>
+      <c r="E3685" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3686" spans="1:5">
+      <c r="A3686" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B3686" s="2" t="s">
+        <v>3466</v>
+      </c>
+      <c r="C3686" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3686" s="2">
+        <v>320.96</v>
+      </c>
+      <c r="E3686" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3687" spans="1:5">
+      <c r="A3687" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3687" s="2" t="s">
+        <v>3467</v>
+      </c>
+      <c r="C3687" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3687" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3687" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3688" spans="1:5">
+      <c r="A3688" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3688" s="2" t="s">
+        <v>3468</v>
+      </c>
+      <c r="C3688" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3688" s="2">
+        <v>572.6</v>
+      </c>
+      <c r="E3688" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3689" spans="1:5">
+      <c r="A3689" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3689" s="2" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C3689" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3689" s="2">
+        <v>494.1</v>
+      </c>
+      <c r="E3689" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3690" spans="1:5">
+      <c r="A3690" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3690" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C3690" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3690" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3690" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3691" spans="1:5">
+      <c r="A3691" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B3691" s="2" t="s">
+        <v>3470</v>
+      </c>
+      <c r="C3691" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3691" s="2">
+        <v>221</v>
+      </c>
+      <c r="E3691" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3692" spans="1:5">
+      <c r="A3692" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3692" s="2" t="s">
+        <v>3471</v>
+      </c>
+      <c r="C3692" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3692" s="2">
+        <v>530.1</v>
+      </c>
+      <c r="E3692" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3693" spans="1:5">
+      <c r="A3693" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3693" s="2" t="s">
+        <v>3472</v>
+      </c>
+      <c r="C3693" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3693" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3693" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3694" spans="1:5">
+      <c r="A3694" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B3694" s="2" t="s">
+        <v>3473</v>
+      </c>
+      <c r="C3694" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3694" s="2">
+        <v>349</v>
+      </c>
+      <c r="E3694" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3695" spans="1:5">
+      <c r="A3695" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3695" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C3695" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3695" s="2">
+        <v>559</v>
+      </c>
+      <c r="E3695" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3696" spans="1:5">
+      <c r="A3696" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B3696" s="2" t="s">
+        <v>3474</v>
+      </c>
+      <c r="C3696" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3696" s="2">
+        <v>399</v>
+      </c>
+      <c r="E3696" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3697" spans="1:5">
+      <c r="A3697" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B3697" s="2" t="s">
+        <v>3475</v>
+      </c>
+      <c r="C3697" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3697" s="2">
+        <v>316</v>
+      </c>
+      <c r="E3697" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3698" spans="1:5">
+      <c r="A3698" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3698" s="2" t="s">
+        <v>3476</v>
+      </c>
+      <c r="C3698" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3698" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3698" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3699" spans="1:5">
+      <c r="A3699" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3699" s="2" t="s">
+        <v>3477</v>
+      </c>
+      <c r="C3699" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3699" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3699" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3700" spans="1:5">
+      <c r="A3700" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3700" s="2" t="s">
+        <v>3478</v>
+      </c>
+      <c r="C3700" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3700" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3700" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3701" spans="1:5">
+      <c r="A3701" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3701" s="2" t="s">
+        <v>3479</v>
+      </c>
+      <c r="C3701" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3701" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3701" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3702" spans="1:5">
+      <c r="A3702" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3702" s="2" t="s">
+        <v>3480</v>
+      </c>
+      <c r="C3702" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3702" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3702" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3703" spans="1:5">
+      <c r="A3703" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3703" s="2" t="s">
+        <v>3481</v>
+      </c>
+      <c r="C3703" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3703" s="2">
+        <v>559</v>
+      </c>
+      <c r="E3703" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3704" spans="1:5">
+      <c r="A3704" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3704" s="2" t="s">
+        <v>3482</v>
+      </c>
+      <c r="C3704" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3704" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3704" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3705" spans="1:5">
+      <c r="A3705" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B3705" s="2" t="s">
+        <v>3483</v>
+      </c>
+      <c r="C3705" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3705" s="2">
+        <v>349</v>
+      </c>
+      <c r="E3705" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3706" spans="1:5">
+      <c r="A3706" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3706" s="2" t="s">
+        <v>3484</v>
+      </c>
+      <c r="C3706" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3706" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3706" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3707" spans="1:5">
+      <c r="A3707" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3707" s="2" t="s">
+        <v>3485</v>
+      </c>
+      <c r="C3707" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3707" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3707" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3708" spans="1:5">
+      <c r="A3708" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B3708" s="2" t="s">
+        <v>3486</v>
+      </c>
+      <c r="C3708" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3708" s="2">
+        <v>399</v>
+      </c>
+      <c r="E3708" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3709" spans="1:5">
+      <c r="A3709" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3709" s="2" t="s">
+        <v>3487</v>
+      </c>
+      <c r="C3709" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3709" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3709" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3710" spans="1:5">
+      <c r="A3710" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3710" s="2" t="s">
+        <v>3488</v>
+      </c>
+      <c r="C3710" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3710" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3710" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3711" spans="1:5">
+      <c r="A3711" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3711" s="2" t="s">
+        <v>3489</v>
+      </c>
+      <c r="C3711" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3711" s="2">
+        <v>536.4</v>
+      </c>
+      <c r="E3711" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3712" spans="1:5">
+      <c r="A3712" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3712" s="2" t="s">
+        <v>3490</v>
+      </c>
+      <c r="C3712" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3712" s="2">
+        <v>512.1</v>
+      </c>
+      <c r="E3712" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3713" spans="1:5">
+      <c r="A3713" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3713" s="2" t="s">
+        <v>3491</v>
+      </c>
+      <c r="C3713" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3713" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3713" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3714" spans="1:5">
+      <c r="A3714" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3714" s="2" t="s">
+        <v>3492</v>
+      </c>
+      <c r="C3714" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3714" s="2">
+        <v>537.3</v>
+      </c>
+      <c r="E3714" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3715" spans="1:5">
+      <c r="A3715" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B3715" s="2" t="s">
+        <v>3493</v>
+      </c>
+      <c r="C3715" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3715" s="2">
+        <v>339</v>
+      </c>
+      <c r="E3715" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3716" spans="1:5">
+      <c r="A3716" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B3716" s="2" t="s">
+        <v>3494</v>
+      </c>
+      <c r="C3716" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3716" s="2">
+        <v>371</v>
+      </c>
+      <c r="E3716" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3717" spans="1:5">
+      <c r="A3717" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3717" s="2" t="s">
+        <v>3495</v>
+      </c>
+      <c r="C3717" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3717" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3717" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3718" spans="1:5">
+      <c r="A3718" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3718" s="2" t="s">
+        <v>3496</v>
+      </c>
+      <c r="C3718" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3718" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3718" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3719" spans="1:5">
+      <c r="A3719" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3719" s="2" t="s">
+        <v>3497</v>
+      </c>
+      <c r="C3719" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3719" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3719" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3720" spans="1:5">
+      <c r="A3720" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3720" s="2" t="s">
+        <v>3498</v>
+      </c>
+      <c r="C3720" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3720" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3720" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3721" spans="1:5">
+      <c r="A3721" s="2" t="s">
+        <v>3499</v>
+      </c>
+      <c r="B3721" s="2" t="s">
+        <v>3500</v>
+      </c>
+      <c r="C3721" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3721" s="3">
+        <v>1399</v>
+      </c>
+      <c r="E3721" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3722" spans="1:5">
+      <c r="A3722" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3722" s="2" t="s">
+        <v>3501</v>
+      </c>
+      <c r="C3722" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3722" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3722" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3723" spans="1:5">
+      <c r="A3723" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B3723" s="2" t="s">
+        <v>3502</v>
+      </c>
+      <c r="C3723" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3723" s="2">
+        <v>395.76</v>
+      </c>
+      <c r="E3723" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3724" spans="1:5">
+      <c r="A3724" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3724" s="2" t="s">
+        <v>3503</v>
+      </c>
+      <c r="C3724" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3724" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3724" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3725" spans="1:5">
+      <c r="A3725" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3725" s="2" t="s">
+        <v>3504</v>
+      </c>
+      <c r="C3725" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3725" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3725" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3726" spans="1:5">
+      <c r="A3726" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3726" s="2" t="s">
+        <v>3505</v>
+      </c>
+      <c r="C3726" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3726" s="2">
+        <v>585</v>
+      </c>
+      <c r="E3726" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3727" spans="1:5">
+      <c r="A3727" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3727" s="2" t="s">
+        <v>3506</v>
+      </c>
+      <c r="C3727" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3727" s="2">
+        <v>529.2</v>
+      </c>
+      <c r="E3727" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3728" spans="1:5">
+      <c r="A3728" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3728" s="2" t="s">
+        <v>3507</v>
+      </c>
+      <c r="C3728" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3728" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3728" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3729" spans="1:5">
+      <c r="A3729" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3729" s="2" t="s">
+        <v>3508</v>
+      </c>
+      <c r="C3729" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3729" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3729" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3730" spans="1:5">
+      <c r="A3730" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3730" s="2" t="s">
+        <v>3509</v>
+      </c>
+      <c r="C3730" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3730" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3730" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3731" spans="1:5">
+      <c r="A3731" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3731" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="C3731" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3731" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3731" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3732" spans="1:5">
+      <c r="A3732" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3732" s="2" t="s">
+        <v>3511</v>
+      </c>
+      <c r="C3732" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3732" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3732" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3733" spans="1:5">
+      <c r="A3733" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3733" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="C3733" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3733" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3733" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3734" spans="1:5">
+      <c r="A3734" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3734" s="2" t="s">
+        <v>3513</v>
+      </c>
+      <c r="C3734" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3734" s="2">
+        <v>589</v>
+      </c>
+      <c r="E3734" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3735" spans="1:5">
+      <c r="A3735" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3735" s="2" t="s">
+        <v>3514</v>
+      </c>
+      <c r="C3735" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3735" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3735" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3736" spans="1:5">
+      <c r="A3736" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3736" s="2" t="s">
+        <v>3515</v>
+      </c>
+      <c r="C3736" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3736" s="2">
+        <v>537.3</v>
+      </c>
+      <c r="E3736" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3737" spans="1:5">
+      <c r="A3737" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3737" s="2" t="s">
+        <v>3516</v>
+      </c>
+      <c r="C3737" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3737" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3737" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3738" spans="1:5">
+      <c r="A3738" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3738" s="2" t="s">
+        <v>3517</v>
+      </c>
+      <c r="C3738" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3738" s="2">
+        <v>535.5</v>
+      </c>
+      <c r="E3738" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3739" spans="1:5">
+      <c r="A3739" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3739" s="2" t="s">
+        <v>3518</v>
+      </c>
+      <c r="C3739" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3739" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3739" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3740" spans="1:5">
+      <c r="A3740" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3740" s="2" t="s">
+        <v>3519</v>
+      </c>
+      <c r="C3740" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3740" s="2">
+        <v>549</v>
+      </c>
+      <c r="E3740" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3741" spans="1:5">
+      <c r="A3741" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3741" s="2" t="s">
+        <v>3520</v>
+      </c>
+      <c r="C3741" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3741" s="2">
+        <v>517.5</v>
+      </c>
+      <c r="E3741" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3742" spans="1:5">
+      <c r="A3742" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3742" s="2" t="s">
+        <v>3521</v>
+      </c>
+      <c r="C3742" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3742" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3742" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3743" spans="1:5">
+      <c r="A3743" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3743" s="2" t="s">
+        <v>3522</v>
+      </c>
+      <c r="C3743" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3743" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3743" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3744" spans="1:5">
+      <c r="A3744" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B3744" s="2" t="s">
+        <v>3523</v>
+      </c>
+      <c r="C3744" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3744" s="2">
+        <v>477</v>
+      </c>
+      <c r="E3744" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3745" spans="1:5">
+      <c r="A3745" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3745" s="2" t="s">
+        <v>3524</v>
+      </c>
+      <c r="C3745" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3745" s="2">
+        <v>537.3</v>
+      </c>
+      <c r="E3745" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3746" spans="1:5">
+      <c r="A3746" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3746" s="2" t="s">
+        <v>3525</v>
+      </c>
+      <c r="C3746" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3746" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3746" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3747" spans="1:5">
+      <c r="A3747" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B3747" s="2" t="s">
+        <v>3526</v>
+      </c>
+      <c r="C3747" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3747" s="2">
+        <v>399</v>
+      </c>
+      <c r="E3747" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3748" spans="1:5">
+      <c r="A3748" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="B3748" s="2" t="s">
+        <v>3527</v>
+      </c>
+      <c r="C3748" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3748" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3748" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3749" spans="1:5">
+      <c r="A3749" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3749" s="2" t="s">
+        <v>3528</v>
+      </c>
+      <c r="C3749" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3749" s="2">
+        <v>597</v>
+      </c>
+      <c r="E3749" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3750" spans="1:5">
+      <c r="A3750" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3750" s="2" t="s">
+        <v>3529</v>
+      </c>
+      <c r="C3750" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3750" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3750" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3751" spans="1:5">
+      <c r="A3751" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B3751" s="2" t="s">
+        <v>3530</v>
+      </c>
+      <c r="C3751" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3751" s="2">
+        <v>399</v>
+      </c>
+      <c r="E3751" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3752" spans="1:5">
+      <c r="A3752" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3752" s="2" t="s">
+        <v>3531</v>
+      </c>
+      <c r="C3752" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3752" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3752" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3753" spans="1:5">
+      <c r="A3753" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B3753" s="2" t="s">
+        <v>3532</v>
+      </c>
+      <c r="C3753" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3753" s="2">
+        <v>597</v>
+      </c>
+      <c r="E3753" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3754" spans="1:5">
+      <c r="A3754" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3754" s="2" t="s">
+        <v>3533</v>
+      </c>
+      <c r="C3754" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3754" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3754" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3755" spans="1:5">
+      <c r="A3755" s="2" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B3755" s="2" t="s">
+        <v>3534</v>
+      </c>
+      <c r="C3755" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3755" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3755" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3756" spans="1:5">
+      <c r="A3756" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3756" s="2" t="s">
+        <v>3535</v>
+      </c>
+      <c r="C3756" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3756" s="2">
+        <v>513.9</v>
+      </c>
+      <c r="E3756" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3757" spans="1:5">
+      <c r="A3757" s="2" t="s">
+        <v>3536</v>
+      </c>
+      <c r="B3757" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C3757" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3757" s="2">
+        <v>33</v>
+      </c>
+      <c r="E3757" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3758" spans="1:5">
+      <c r="A3758" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3758" s="2" t="s">
+        <v>3537</v>
+      </c>
+      <c r="C3758" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3758" s="2">
+        <v>533.7</v>
+      </c>
+      <c r="E3758" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3759" spans="1:5">
+      <c r="A3759" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3759" s="2" t="s">
+        <v>3538</v>
+      </c>
+      <c r="C3759" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3759" s="2">
+        <v>537.3</v>
+      </c>
+      <c r="E3759" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3760" spans="1:5">
+      <c r="A3760" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3760" s="2" t="s">
+        <v>3539</v>
+      </c>
+      <c r="C3760" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3760" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3760" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3761" spans="1:5">
+      <c r="A3761" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3761" s="2" t="s">
+        <v>3540</v>
+      </c>
+      <c r="C3761" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3761" s="2">
+        <v>530.1</v>
+      </c>
+      <c r="E3761" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3762" spans="1:5">
+      <c r="A3762" s="2" t="s">
+        <v>3453</v>
+      </c>
+      <c r="B3762" s="2" t="s">
+        <v>3541</v>
+      </c>
+      <c r="C3762" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3762" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="E3762" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3763" spans="1:5">
+      <c r="A3763" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3763" s="2" t="s">
+        <v>3542</v>
+      </c>
+      <c r="C3763" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3763" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3763" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3764" spans="1:5">
+      <c r="A3764" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3764" s="2" t="s">
+        <v>3543</v>
+      </c>
+      <c r="C3764" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3764" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3764" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3765" spans="1:5">
+      <c r="A3765" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3765" s="2" t="s">
+        <v>3544</v>
+      </c>
+      <c r="C3765" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3765" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3765" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3766" spans="1:5">
+      <c r="A3766" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3766" s="2" t="s">
+        <v>3545</v>
+      </c>
+      <c r="C3766" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3766" s="2">
+        <v>534.6</v>
+      </c>
+      <c r="E3766" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3767" spans="1:5">
+      <c r="A3767" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3767" s="2" t="s">
+        <v>3546</v>
+      </c>
+      <c r="C3767" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3767" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3767" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3768" spans="1:5">
+      <c r="A3768" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B3768" s="2" t="s">
+        <v>3547</v>
+      </c>
+      <c r="C3768" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3768" s="2">
+        <v>399</v>
+      </c>
+      <c r="E3768" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3769" spans="1:5">
+      <c r="A3769" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3769" s="2" t="s">
+        <v>3548</v>
+      </c>
+      <c r="C3769" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3769" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3769" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3770" spans="1:5">
+      <c r="A3770" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3770" s="2" t="s">
+        <v>3549</v>
+      </c>
+      <c r="C3770" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3770" s="2">
+        <v>514.8</v>
+      </c>
+      <c r="E3770" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3771" spans="1:5">
+      <c r="A3771" s="2" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B3771" s="2" t="s">
+        <v>3550</v>
+      </c>
+      <c r="C3771" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3771" s="2">
+        <v>549</v>
+      </c>
+      <c r="E3771" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3772" spans="1:5">
+      <c r="A3772" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3772" s="2" t="s">
+        <v>3551</v>
+      </c>
+      <c r="C3772" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3772" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3772" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3773" spans="1:5">
+      <c r="A3773" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3773" s="2" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C3773" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3773" s="2">
+        <v>560</v>
+      </c>
+      <c r="E3773" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3774" spans="1:5">
+      <c r="A3774" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B3774" s="2" t="s">
+        <v>3552</v>
+      </c>
+      <c r="C3774" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3774" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3774" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3775" spans="1:5">
+      <c r="A3775" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3775" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C3775" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3775" s="2">
+        <v>594</v>
+      </c>
+      <c r="E3775" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3776" spans="1:5">
+      <c r="A3776" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3776" s="2" t="s">
+        <v>3553</v>
+      </c>
+      <c r="C3776" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3776" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3776" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3777" spans="1:5">
+      <c r="A3777" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B3777" s="2" t="s">
+        <v>3554</v>
+      </c>
+      <c r="C3777" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3777" s="2">
+        <v>349</v>
+      </c>
+      <c r="E3777" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3778" spans="1:5">
+      <c r="A3778" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3778" s="2" t="s">
+        <v>3555</v>
+      </c>
+      <c r="C3778" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3778" s="2">
+        <v>549</v>
+      </c>
+      <c r="E3778" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3779" spans="1:5">
+      <c r="A3779" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B3779" s="2" t="s">
+        <v>3556</v>
+      </c>
+      <c r="C3779" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3779" s="2">
+        <v>240.5</v>
+      </c>
+      <c r="E3779" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3780" spans="1:5">
+      <c r="A3780" s="2" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B3780" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C3780" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3780" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3780" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3781" spans="1:5">
+      <c r="A3781" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3781" s="2" t="s">
+        <v>3557</v>
+      </c>
+      <c r="C3781" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3781" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3781" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3782" spans="1:5">
+      <c r="A3782" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B3782" s="2" t="s">
+        <v>3558</v>
+      </c>
+      <c r="C3782" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3782" s="2">
+        <v>247</v>
+      </c>
+      <c r="E3782" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3783" spans="1:5">
+      <c r="A3783" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B3783" s="2" t="s">
+        <v>3559</v>
+      </c>
+      <c r="C3783" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3783" s="2">
+        <v>371</v>
+      </c>
+      <c r="E3783" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3784" spans="1:5">
+      <c r="A3784" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3784" s="2" t="s">
+        <v>3560</v>
+      </c>
+      <c r="C3784" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3784" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3784" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3785" spans="1:5">
+      <c r="A3785" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3785" s="2" t="s">
+        <v>3561</v>
+      </c>
+      <c r="C3785" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3785" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3785" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3786" spans="1:5">
+      <c r="A3786" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3786" s="2" t="s">
+        <v>3562</v>
+      </c>
+      <c r="C3786" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3786" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3786" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3787" spans="1:5">
+      <c r="A3787" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3787" s="2" t="s">
+        <v>3563</v>
+      </c>
+      <c r="C3787" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3787" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3787" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3788" spans="1:5">
+      <c r="A3788" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3788" s="2" t="s">
+        <v>3564</v>
+      </c>
+      <c r="C3788" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3788" s="2">
+        <v>537.3</v>
+      </c>
+      <c r="E3788" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3789" spans="1:5">
+      <c r="A3789" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B3789" s="2" t="s">
+        <v>3565</v>
+      </c>
+      <c r="C3789" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3789" s="2">
+        <v>379</v>
+      </c>
+      <c r="E3789" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3790" spans="1:5">
+      <c r="A3790" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3790" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="C3790" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3790" s="2">
+        <v>576</v>
+      </c>
+      <c r="E3790" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3791" spans="1:5">
+      <c r="A3791" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3791" s="2" t="s">
+        <v>3566</v>
+      </c>
+      <c r="C3791" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3791" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3791" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3792" spans="1:5">
+      <c r="A3792" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B3792" s="2" t="s">
+        <v>3567</v>
+      </c>
+      <c r="C3792" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3792" s="2">
+        <v>229</v>
+      </c>
+      <c r="E3792" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3793" spans="1:5">
+      <c r="A3793" s="2" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B3793" s="2" t="s">
+        <v>2742</v>
+      </c>
+      <c r="C3793" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3793" s="2">
+        <v>479</v>
+      </c>
+      <c r="E3793" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3794" spans="1:5">
+      <c r="A3794" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B3794" s="2" t="s">
+        <v>3568</v>
+      </c>
+      <c r="C3794" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3794" s="2">
+        <v>269</v>
+      </c>
+      <c r="E3794" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3795" spans="1:5">
+      <c r="A3795" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3795" s="2" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C3795" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3795" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3795" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3796" spans="1:5">
+      <c r="A3796" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3796" s="2" t="s">
+        <v>3570</v>
+      </c>
+      <c r="C3796" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3796" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3796" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3797" spans="1:5">
+      <c r="A3797" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3797" s="2" t="s">
+        <v>3571</v>
+      </c>
+      <c r="C3797" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3797" s="2">
+        <v>494.1</v>
+      </c>
+      <c r="E3797" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3798" spans="1:5">
+      <c r="A3798" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3798" s="2" t="s">
+        <v>3572</v>
+      </c>
+      <c r="C3798" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3798" s="2">
+        <v>597</v>
+      </c>
+      <c r="E3798" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3799" spans="1:5">
+      <c r="A3799" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3799" s="2" t="s">
+        <v>3573</v>
+      </c>
+      <c r="C3799" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3799" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3799" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3800" spans="1:5">
+      <c r="A3800" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3800" s="2" t="s">
+        <v>3064</v>
+      </c>
+      <c r="C3800" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3800" s="2">
+        <v>548.96</v>
+      </c>
+      <c r="E3800" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3801" spans="1:5">
+      <c r="A3801" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3801" s="2" t="s">
+        <v>3574</v>
+      </c>
+      <c r="C3801" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3801" s="2">
+        <v>568</v>
+      </c>
+      <c r="E3801" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3802" spans="1:5">
+      <c r="A3802" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B3802" s="2" t="s">
+        <v>3575</v>
+      </c>
+      <c r="C3802" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3802" s="2">
+        <v>218.07</v>
+      </c>
+      <c r="E3802" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3803" spans="1:5">
+      <c r="A3803" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3803" s="2" t="s">
+        <v>3576</v>
+      </c>
+      <c r="C3803" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3803" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3803" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3804" spans="1:5">
+      <c r="A3804" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3804" s="2" t="s">
+        <v>3577</v>
+      </c>
+      <c r="C3804" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3804" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3804" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3805" spans="1:5">
+      <c r="A3805" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3805" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C3805" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3805" s="2">
+        <v>537.3</v>
+      </c>
+      <c r="E3805" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3806" spans="1:5">
+      <c r="A3806" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3806" s="2" t="s">
+        <v>3578</v>
+      </c>
+      <c r="C3806" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3806" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3806" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3807" spans="1:5">
+      <c r="A3807" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3807" s="2" t="s">
+        <v>3579</v>
+      </c>
+      <c r="C3807" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3807" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3807" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3808" spans="1:5">
+      <c r="A3808" s="2" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B3808" s="2" t="s">
+        <v>3580</v>
+      </c>
+      <c r="C3808" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3808" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3808" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3809" spans="1:5">
+      <c r="A3809" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3809" s="2" t="s">
+        <v>3581</v>
+      </c>
+      <c r="C3809" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3809" s="2">
+        <v>541.4</v>
+      </c>
+      <c r="E3809" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3810" spans="1:5">
+      <c r="A3810" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3810" s="2" t="s">
+        <v>3582</v>
+      </c>
+      <c r="C3810" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3810" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3810" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3811" spans="1:5">
+      <c r="A3811" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3811" s="2" t="s">
+        <v>3583</v>
+      </c>
+      <c r="C3811" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3811" s="2">
+        <v>529.2</v>
+      </c>
+      <c r="E3811" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3812" spans="1:5">
+      <c r="A3812" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3812" s="2" t="s">
+        <v>3584</v>
+      </c>
+      <c r="C3812" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3812" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3812" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3813" spans="1:5">
+      <c r="A3813" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B3813" s="2" t="s">
+        <v>3585</v>
+      </c>
+      <c r="C3813" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3813" s="2">
+        <v>352</v>
+      </c>
+      <c r="E3813" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3814" spans="1:5">
+      <c r="A3814" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B3814" s="2" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C3814" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3814" s="2">
+        <v>219</v>
+      </c>
+      <c r="E3814" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3815" spans="1:5">
+      <c r="A3815" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3815" s="2" t="s">
+        <v>3587</v>
+      </c>
+      <c r="C3815" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3815" s="2">
+        <v>597</v>
+      </c>
+      <c r="E3815" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3816" spans="1:5">
+      <c r="A3816" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3816" s="2" t="s">
+        <v>3588</v>
+      </c>
+      <c r="C3816" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3816" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3816" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3817" spans="1:5">
+      <c r="A3817" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3817" s="2" t="s">
+        <v>3589</v>
+      </c>
+      <c r="C3817" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D3817" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3817" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3818" spans="1:5">
+      <c r="A3818" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3818" s="2" t="s">
+        <v>3590</v>
+      </c>
+      <c r="C3818" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3818" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3818" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3819" spans="1:5">
+      <c r="A3819" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B3819" s="2" t="s">
+        <v>3591</v>
+      </c>
+      <c r="C3819" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3819" s="2">
+        <v>549</v>
+      </c>
+      <c r="E3819" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3820" spans="1:5">
+      <c r="A3820" s="2" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B3820" s="2" t="s">
+        <v>3401</v>
+      </c>
+      <c r="C3820" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3820" s="2">
+        <v>584</v>
+      </c>
+      <c r="E3820" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3821" spans="1:5">
+      <c r="A3821" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B3821" s="2" t="s">
+        <v>3592</v>
+      </c>
+      <c r="C3821" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3821" s="2">
+        <v>349</v>
+      </c>
+      <c r="E3821" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3822" spans="1:5">
+      <c r="A3822" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3822" s="2" t="s">
+        <v>3593</v>
+      </c>
+      <c r="C3822" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3822" s="2">
+        <v>597</v>
+      </c>
+      <c r="E3822" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3823" spans="1:5">
+      <c r="A3823" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3823" s="2" t="s">
+        <v>3594</v>
+      </c>
+      <c r="C3823" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3823" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3823" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3824" spans="1:5">
+      <c r="A3824" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3824" s="2" t="s">
+        <v>3595</v>
+      </c>
+      <c r="C3824" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3824" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3824" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3825" spans="1:5">
+      <c r="A3825" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B3825" s="2" t="s">
+        <v>3596</v>
+      </c>
+      <c r="C3825" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3825" s="2">
+        <v>348.78</v>
+      </c>
+      <c r="E3825" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3826" spans="1:5">
+      <c r="A3826" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B3826" s="2" t="s">
+        <v>3597</v>
+      </c>
+      <c r="C3826" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3826" s="2">
+        <v>379.05</v>
+      </c>
+      <c r="E3826" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3827" spans="1:5">
+      <c r="A3827" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B3827" s="2" t="s">
+        <v>3598</v>
+      </c>
+      <c r="C3827" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3827" s="2">
+        <v>322.6</v>
+      </c>
+      <c r="E3827" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3828" spans="1:5">
+      <c r="A3828" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3828" s="2" t="s">
+        <v>3599</v>
+      </c>
+      <c r="C3828" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3828" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3828" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3829" spans="1:5">
+      <c r="A3829" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3829" s="2" t="s">
+        <v>3600</v>
+      </c>
+      <c r="C3829" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3829" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3829" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3830" spans="1:5">
+      <c r="A3830" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3830" s="2" t="s">
+        <v>3601</v>
+      </c>
+      <c r="C3830" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3830" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3830" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3831" spans="1:5">
+      <c r="A3831" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3831" s="2" t="s">
+        <v>3602</v>
+      </c>
+      <c r="C3831" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3831" s="2">
+        <v>494.1</v>
+      </c>
+      <c r="E3831" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3832" spans="1:5">
+      <c r="A3832" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3832" s="2" t="s">
+        <v>3603</v>
+      </c>
+      <c r="C3832" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3832" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3832" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3833" spans="1:5">
+      <c r="A3833" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B3833" s="2" t="s">
+        <v>3604</v>
+      </c>
+      <c r="C3833" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3833" s="2">
+        <v>184.35</v>
+      </c>
+      <c r="E3833" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3834" spans="1:5">
+      <c r="A3834" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3834" s="2" t="s">
+        <v>3605</v>
+      </c>
+      <c r="C3834" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3834" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3834" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3835" spans="1:5">
+      <c r="A3835" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3835" s="2" t="s">
+        <v>3606</v>
+      </c>
+      <c r="C3835" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3835" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3835" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3836" spans="1:5">
+      <c r="A3836" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3836" s="2" t="s">
+        <v>3607</v>
+      </c>
+      <c r="C3836" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3836" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3836" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3837" spans="1:5">
+      <c r="A3837" s="2" t="s">
+        <v>3536</v>
+      </c>
+      <c r="B3837" s="2" t="s">
+        <v>3608</v>
+      </c>
+      <c r="C3837" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3837" s="2">
+        <v>32</v>
+      </c>
+      <c r="E3837" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3838" spans="1:5">
+      <c r="A3838" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3838" s="2" t="s">
+        <v>3609</v>
+      </c>
+      <c r="C3838" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3838" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3838" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3839" spans="1:5">
+      <c r="A3839" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3839" s="2" t="s">
+        <v>3610</v>
+      </c>
+      <c r="C3839" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3839" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3839" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3840" spans="1:5">
+      <c r="A3840" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3840" s="2" t="s">
+        <v>3611</v>
+      </c>
+      <c r="C3840" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3840" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3840" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3841" spans="1:5">
+      <c r="A3841" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3841" s="2" t="s">
+        <v>3612</v>
+      </c>
+      <c r="C3841" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3841" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3841" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3842" spans="1:5">
+      <c r="A3842" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3842" s="2" t="s">
+        <v>3613</v>
+      </c>
+      <c r="C3842" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3842" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3842" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3843" spans="1:5">
+      <c r="A3843" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3843" s="2" t="s">
+        <v>3614</v>
+      </c>
+      <c r="C3843" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3843" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3843" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3844" spans="1:5">
+      <c r="A3844" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3844" s="2" t="s">
+        <v>3615</v>
+      </c>
+      <c r="C3844" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3844" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3844" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3845" spans="1:5">
+      <c r="A3845" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B3845" s="2" t="s">
+        <v>3616</v>
+      </c>
+      <c r="C3845" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3845" s="2">
+        <v>399</v>
+      </c>
+      <c r="E3845" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3846" spans="1:5">
+      <c r="A3846" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3846" s="2" t="s">
+        <v>3617</v>
+      </c>
+      <c r="C3846" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3846" s="2">
+        <v>599</v>
+      </c>
+      <c r="E3846" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3847" spans="1:5">
+      <c r="A3847" s="2" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3847" s="2" t="s">
+        <v>3618</v>
+      </c>
+      <c r="C3847" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3847" s="2">
+        <v>538.2</v>
+      </c>
+      <c r="E3847" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="3848" spans="1:5">
+      <c r="A3848" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3848" s="2" t="s">
+        <v>3619</v>
+      </c>
+      <c r="C3848" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3848" s="2">
+        <v>539.1</v>
+      </c>
+      <c r="E3848" s="2" t="s">
+        <v>3415</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
